--- a/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4068,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7348,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4068,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7348,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4068,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7348,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -778,6 +778,8 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -790,7 +792,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -845,6 +847,16 @@
           <t>BandaConvRate</t>
         </is>
       </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Eficacia_WoW_pp</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>ConvRate_WoW_pp</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -887,6 +899,10 @@
           <t>Revisar</t>
         </is>
       </c>
+      <c r="K6" s="5" t="n">
+        <v>-29.47574044968526</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -929,6 +945,10 @@
           <t>Aceptable</t>
         </is>
       </c>
+      <c r="K7" s="5" t="n">
+        <v>-4.622372639828997</v>
+      </c>
+      <c r="L7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -971,6 +991,10 @@
           <t>Exitosa</t>
         </is>
       </c>
+      <c r="K8" s="5" t="n">
+        <v>-9.622733583515469</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1013,6 +1037,12 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K9" s="5" t="n">
+        <v>-9.248977206312098</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>0.1356767137012607</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1055,6 +1085,8 @@
           <t>Exitosa</t>
         </is>
       </c>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1097,6 +1129,10 @@
           <t>Aceptable</t>
         </is>
       </c>
+      <c r="K11" s="5" t="n">
+        <v>3.451963622259546</v>
+      </c>
+      <c r="L11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1139,6 +1175,8 @@
           <t>Aceptable</t>
         </is>
       </c>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1181,6 +1219,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K13" s="5" t="n">
+        <v>6.478567189051598</v>
+      </c>
+      <c r="L13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1223,6 +1265,8 @@
           <t>Exitosa</t>
         </is>
       </c>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1264,6 +1308,12 @@
         <is>
           <t>Revisar</t>
         </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.8804080745265286</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>0.1820296251933103</v>
       </c>
     </row>
   </sheetData>
@@ -1277,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1290,6 +1340,8 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1302,7 +1354,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1357,6 +1409,16 @@
           <t>BandaConvRate</t>
         </is>
       </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Eficacia_WoW_pp</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>ConvRate_WoW_pp</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1399,6 +1461,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="n">
+        <v>0.1155882822636469</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1441,6 +1507,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="n">
+        <v>0.03099040237947146</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1483,6 +1553,8 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1525,6 +1597,8 @@
           <t>Revisar</t>
         </is>
       </c>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1567,6 +1641,8 @@
           <t>Revisar</t>
         </is>
       </c>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1609,6 +1685,8 @@
           <t>Revisar</t>
         </is>
       </c>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1651,6 +1729,8 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1693,6 +1773,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="n">
+        <v>-0.2989990861091568</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1735,6 +1819,8 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1777,6 +1863,8 @@
           <t>Revisar</t>
         </is>
       </c>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1789,7 +1877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1802,6 +1890,8 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1814,7 +1904,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1869,6 +1959,16 @@
           <t>BandaConvRate</t>
         </is>
       </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Eficacia_WoW_pp</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>ConvRate_WoW_pp</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1911,6 +2011,12 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K6" s="5" t="n">
+        <v>8.862216321910266</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>-0.1415207831763742</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1953,6 +2059,8 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1995,6 +2103,12 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K8" s="5" t="n">
+        <v>-3.89972722603753</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0.05331501798262291</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2037,6 +2151,10 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K9" s="5" t="n">
+        <v>-5.374945299757328</v>
+      </c>
+      <c r="L9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2079,6 +2197,12 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K10" s="5" t="n">
+        <v>-8.965678804109272</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0.05770340450086555</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2121,6 +2245,8 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2163,6 +2289,10 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="n">
+        <v>-0.07424023551101927</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -2205,6 +2335,8 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -2247,6 +2379,8 @@
           <t>Sin Conversión</t>
         </is>
       </c>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2288,6 +2422,10 @@
         <is>
           <t>Sin Conversión</t>
         </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="n">
+        <v>-0.09945978019145403</v>
       </c>
     </row>
   </sheetData>
@@ -2301,7 +2439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2314,6 +2452,8 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2326,7 +2466,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2381,6 +2521,16 @@
           <t>BandaConvRate</t>
         </is>
       </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Eficacia_WoW_pp</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>ConvRate_WoW_pp</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2423,6 +2573,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="n">
+        <v>-0.2989990861091568</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2465,6 +2619,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="n">
+        <v>-0.2839562791408698</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2507,6 +2665,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="n">
+        <v>0.03099040237947146</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2549,6 +2711,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="n">
+        <v>0.02534218211934963</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2591,6 +2757,8 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2633,6 +2801,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="n">
+        <v>0.1155882822636469</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2675,6 +2847,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="n">
+        <v>0.3636363636363636</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -2717,6 +2893,8 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -2759,6 +2937,10 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="n">
+        <v>-0.4006635990859862</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2801,6 +2983,8 @@
           <t>Crítica</t>
         </is>
       </c>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2836,7 +3020,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4252,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7532,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -7532,7 +7532,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,6 +150,8 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -533,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -658,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -792,7 +794,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -874,19 +876,19 @@
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="11" t="n">
         <v>589</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="11" t="n">
         <v>201</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="12" t="n">
         <v>0.3412563667232598</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="12" t="n">
         <v>0.01188455008488964</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -920,19 +922,19 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="11" t="n">
         <v>401</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="11" t="n">
         <v>139</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="12" t="n">
         <v>0.3466334164588529</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="12" t="n">
         <v>0.02493765586034913</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -966,19 +968,19 @@
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="11" t="n">
         <v>584</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="11" t="n">
         <v>205</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="12" t="n">
         <v>0.351027397260274</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="12" t="n">
         <v>0.02910958904109589</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1012,19 +1014,19 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="11" t="n">
         <v>331</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="11" t="n">
         <v>135</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="12" t="n">
         <v>0.4078549848942598</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="12" t="n">
         <v>0.006042296072507553</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1060,19 +1062,19 @@
           <t>Melbourne Area</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="11" t="n">
         <v>165</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="11" t="n">
         <v>77</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="12" t="n">
         <v>0.4666666666666667</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="12" t="n">
         <v>0.1575757575757576</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1104,19 +1106,19 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="11" t="n">
         <v>3587</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="11" t="n">
         <v>78</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="11" t="n">
         <v>2013</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="12" t="n">
         <v>0.5611931976582102</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="12" t="n">
         <v>0.02174519096738221</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -1150,19 +1152,19 @@
           <t>San Andres, Providencia y Santa Catalina</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="11" t="n">
         <v>164</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="11" t="n">
         <v>94</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="12" t="n">
         <v>0.573170731707317</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="12" t="n">
         <v>0.01829268292682927</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1194,19 +1196,19 @@
           <t>Tokyo</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="11" t="n">
         <v>454</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="11" t="n">
         <v>285</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="12" t="n">
         <v>0.6277533039647577</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="12" t="n">
         <v>0.004405286343612335</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1240,19 +1242,19 @@
           <t>Puerto Vallarta Area</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="11" t="n">
         <v>192</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="11" t="n">
         <v>126</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="12" t="n">
         <v>0.65625</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="12" t="n">
         <v>0.09375</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1284,19 +1286,19 @@
           <t>Montreal</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="11" t="n">
         <v>272</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="11" t="n">
         <v>180</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="12" t="n">
         <v>0.6617647058823529</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="12" t="n">
         <v>0.01102941176470588</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1354,7 +1356,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1436,19 +1438,19 @@
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="11" t="n">
         <v>2835</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="11" t="n">
         <v>2828</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="12" t="n">
         <v>0.9975308641975309</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="12" t="n">
         <v>0.002821869488536155</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -1482,19 +1484,19 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="11" t="n">
         <v>2402</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="11" t="n">
         <v>2297</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="12" t="n">
         <v>0.9562864279766861</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="12" t="n">
         <v>0.001665278934221482</v>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -1528,19 +1530,19 @@
           <t>Riviera Maya</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="11" t="n">
         <v>1809</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="11" t="n">
         <v>1808</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="12" t="n">
         <v>0.9994472084024323</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="12" t="n">
         <v>0.006633499170812604</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -1572,19 +1574,19 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="11" t="n">
         <v>1050</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="11" t="n">
         <v>1024</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="12" t="n">
         <v>0.9752380952380952</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="12" t="n">
         <v>0.01238095238095238</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -1616,19 +1618,19 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="11" t="n">
         <v>1018</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="11" t="n">
         <v>993</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="12" t="n">
         <v>0.9754420432220039</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="12" t="n">
         <v>0.01178781925343811</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
@@ -1660,19 +1662,19 @@
           <t>Londres</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="11" t="n">
         <v>919</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="11" t="n">
         <v>855</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="12" t="n">
         <v>0.9303590859630033</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="12" t="n">
         <v>0.009793253536452665</v>
       </c>
       <c r="I11" s="8" t="inlineStr">
@@ -1704,19 +1706,19 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="11" t="n">
         <v>888</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="11" t="n">
         <v>875</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="12" t="n">
         <v>0.9853603603603603</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="12" t="n">
         <v>0.00563063063063063</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -1748,19 +1750,19 @@
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="11" t="n">
         <v>875</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="11" t="n">
         <v>870</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="12" t="n">
         <v>0.9942857142857143</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="12" t="n">
         <v>0.001142857142857143</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -1794,19 +1796,19 @@
           <t>Niagara Falls, Canada</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="11" t="n">
         <v>847</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="11" t="n">
         <v>842</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="12" t="n">
         <v>0.9940968122786304</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="12" t="n">
         <v>0.007083825265643448</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -1838,19 +1840,19 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="11" t="n">
         <v>834</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="11" t="n">
         <v>834</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="12" t="n">
         <v>0.008393285371702638</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
@@ -1904,7 +1906,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -1986,19 +1988,19 @@
           <t>San Diego</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="11" t="n">
         <v>1016</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="11" t="n">
         <v>856</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="12" t="n">
         <v>0.84251968503937</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -2034,19 +2036,19 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="11" t="n">
         <v>568</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="11" t="n">
         <v>93</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="12" t="n">
         <v>0.1637323943661972</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -2078,19 +2080,19 @@
           <t>Atenas</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="11" t="n">
         <v>550</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="12" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -2126,19 +2128,19 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="11" t="n">
         <v>532</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="11" t="n">
         <v>478</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="12" t="n">
         <v>0.8984962406015038</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -2172,19 +2174,19 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="11" t="n">
         <v>490</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="12" t="n">
         <v>0.006122448979591836</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -2220,19 +2222,19 @@
           <t>Tbilisi Area</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="11" t="n">
         <v>448</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="11" t="n">
         <v>435</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="12" t="n">
         <v>0.9709821428571429</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -2264,19 +2266,19 @@
           <t>Anaheim Area</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="11" t="n">
         <v>444</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="11" t="n">
         <v>441</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="12" t="n">
         <v>0.9932432432432432</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -2310,19 +2312,19 @@
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="11" t="n">
         <v>440</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="11" t="n">
         <v>434</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="12" t="n">
         <v>0.9863636363636363</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -2354,19 +2356,19 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="11" t="n">
         <v>438</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="11" t="n">
         <v>41</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="12" t="n">
         <v>0.09360730593607305</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -2398,19 +2400,19 @@
           <t>Atlanta Area</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="11" t="n">
         <v>434</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="11" t="n">
         <v>430</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="12" t="n">
         <v>0.9907834101382489</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -2466,7 +2468,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -2548,19 +2550,19 @@
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="11" t="n">
         <v>875</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="11" t="n">
         <v>870</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="12" t="n">
         <v>0.9942857142857143</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="12" t="n">
         <v>0.001142857142857143</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -2594,19 +2596,19 @@
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="11" t="n">
         <v>625</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="11" t="n">
         <v>621</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="12" t="n">
         <v>0.9936</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="12" t="n">
         <v>0.0016</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -2640,19 +2642,19 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="11" t="n">
         <v>2402</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="11" t="n">
         <v>2297</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="12" t="n">
         <v>0.9562864279766861</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="12" t="n">
         <v>0.001665278934221482</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -2686,19 +2688,19 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="11" t="n">
         <v>489</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="11" t="n">
         <v>482</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="12" t="n">
         <v>0.9856850715746421</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="12" t="n">
         <v>0.002044989775051125</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -2732,19 +2734,19 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="11" t="n">
         <v>389</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="11" t="n">
         <v>380</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="12" t="n">
         <v>0.9768637532133676</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="12" t="n">
         <v>0.002570694087403599</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -2776,19 +2778,19 @@
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="11" t="n">
         <v>2835</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="11" t="n">
         <v>2828</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="12" t="n">
         <v>0.9975308641975309</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="12" t="n">
         <v>0.002821869488536155</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -2822,19 +2824,19 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="11" t="n">
         <v>344</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="11" t="n">
         <v>329</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="12" t="n">
         <v>0.9563953488372093</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="12" t="n">
         <v>0.002906976744186046</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -2868,19 +2870,19 @@
           <t>Boston</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="11" t="n">
         <v>343</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="11" t="n">
         <v>338</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="12" t="n">
         <v>0.9854227405247813</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="12" t="n">
         <v>0.002915451895043732</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -2912,19 +2914,19 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="11" t="n">
         <v>324</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="11" t="n">
         <v>323</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="12" t="n">
         <v>0.9969135802469136</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="12" t="n">
         <v>0.00308641975308642</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -2958,19 +2960,19 @@
           <t>Tokyo</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="11" t="n">
         <v>308</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="11" t="n">
         <v>294</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="12" t="n">
         <v>0.9545454545454546</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="12" t="n">
         <v>0.003246753246753247</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -3020,7 +3022,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -3072,19 +3074,19 @@
           <t>IHG</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="11" t="n">
         <v>31994</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="11" t="n">
         <v>743</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>28591</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="12" t="n">
         <v>0.8936363068075264</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="12" t="n">
         <v>0.02322310433206226</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -3104,19 +3106,19 @@
           <t>Hyatt</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="11" t="n">
         <v>20598</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="11" t="n">
         <v>261</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>19791</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="12" t="n">
         <v>0.9608214389746578</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="12" t="n">
         <v>0.01267113311972036</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -3136,19 +3138,19 @@
           <t>Hilton</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="11" t="n">
         <v>20108</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="11" t="n">
         <v>401</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>19829</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="12" t="n">
         <v>0.9861249254028247</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="12" t="n">
         <v>0.01994231151780386</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -3168,19 +3170,19 @@
           <t>AA-Independent</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="11" t="n">
         <v>10853</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="11" t="n">
         <v>513</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>8033</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="12" t="n">
         <v>0.7401640099511656</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="12" t="n">
         <v>0.04726803648760711</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -3200,19 +3202,19 @@
           <t>Caesars Entertainment</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="11" t="n">
         <v>6490</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="11" t="n">
         <v>196</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>4867</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="12" t="n">
         <v>0.7499229583975346</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="12" t="n">
         <v>0.03020030816640986</v>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -3232,19 +3234,19 @@
           <t>MGM Resorts</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="11" t="n">
         <v>5028</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="11" t="n">
         <v>129</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>4965</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="12" t="n">
         <v>0.9874701670644391</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="12" t="n">
         <v>0.0256563245823389</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -3264,19 +3266,19 @@
           <t>Accor</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="11" t="n">
         <v>2982</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="11" t="n">
         <v>15</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>2861</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="12" t="n">
         <v>0.9594232059020792</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="12" t="n">
         <v>0.005030181086519115</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -3296,19 +3298,19 @@
           <t>Palladium Hotel Group</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="11" t="n">
         <v>2274</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="11" t="n">
         <v>276</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>2274</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="12" t="n">
         <v>0.1213720316622691</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -3328,19 +3330,19 @@
           <t>Hoteles Xcaret</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="11" t="n">
         <v>2185</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="11" t="n">
         <v>24</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>2184</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="12" t="n">
         <v>0.9995423340961098</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="12" t="n">
         <v>0.01098398169336384</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -3360,19 +3362,19 @@
           <t>Barcelo</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="11" t="n">
         <v>1687</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="11" t="n">
         <v>112</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>1672</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="12" t="n">
         <v>0.991108476585655</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="12" t="n">
         <v>0.06639004149377593</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -3392,19 +3394,19 @@
           <t>Universal</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="11" t="n">
         <v>1537</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="11" t="n">
         <v>25</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>1473</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="12" t="n">
         <v>0.9583604424202993</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="12" t="n">
         <v>0.01626545217957059</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -3424,19 +3426,19 @@
           <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="11" t="n">
         <v>1336</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="11" t="n">
         <v>54</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>1303</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="12" t="n">
         <v>0.9752994011976048</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="12" t="n">
         <v>0.04041916167664671</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -3456,19 +3458,19 @@
           <t>Palace</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="11" t="n">
         <v>1266</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="11" t="n">
         <v>114</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>1257</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="12" t="n">
         <v>0.9928909952606635</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="12" t="n">
         <v>0.09004739336492891</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -3488,19 +3490,19 @@
           <t>RIU</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="11" t="n">
         <v>1226</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="11" t="n">
         <v>41</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>1226</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="12" t="n">
         <v>0.033442088091354</v>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -3520,19 +3522,19 @@
           <t>Las Brisas</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="11" t="n">
         <v>1205</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="11" t="n">
         <v>83</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>1187</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="12" t="n">
         <v>0.9850622406639005</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="12" t="n">
         <v>0.06887966804979254</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -3552,19 +3554,19 @@
           <t>Bahia Principe</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="11" t="n">
         <v>1177</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="11" t="n">
         <v>89</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>1168</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E21" s="12" t="n">
         <v>0.9923534409515717</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F21" s="12" t="n">
         <v>0.07561597281223449</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -3584,19 +3586,19 @@
           <t>Disney</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="11" t="n">
         <v>910</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="11" t="n">
         <v>11</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>910</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F22" s="12" t="n">
         <v>0.01208791208791209</v>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -3616,19 +3618,19 @@
           <t>Royalton Hotels &amp; Resorts</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="11" t="n">
         <v>891</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="11" t="n">
         <v>45</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>834</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="12" t="n">
         <v>0.936026936026936</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="12" t="n">
         <v>0.0505050505050505</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -3648,19 +3650,19 @@
           <t>Park Royal</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="11" t="n">
         <v>830</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="11" t="n">
         <v>18</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>819</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="12" t="n">
         <v>0.9867469879518073</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="12" t="n">
         <v>0.02168674698795181</v>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -3680,19 +3682,19 @@
           <t>Wyndham</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="11" t="n">
         <v>727</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="11" t="n">
         <v>38</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>701</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="12" t="n">
         <v>0.9642365887207703</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="12" t="n">
         <v>0.05226960110041266</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -3712,19 +3714,19 @@
           <t>Karisma</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="11" t="n">
         <v>634</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="11" t="n">
         <v>19</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>626</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="12" t="n">
         <v>0.9873817034700315</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" s="12" t="n">
         <v>0.02996845425867508</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -3744,19 +3746,19 @@
           <t>Oasis</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="11" t="n">
         <v>616</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="11" t="n">
         <v>6</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>612</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="12" t="n">
         <v>0.9935064935064936</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="12" t="n">
         <v>0.00974025974025974</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -3776,19 +3778,19 @@
           <t>Wynn Las Vegas</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="11" t="n">
         <v>613</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="11" t="n">
         <v>26</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>611</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="12" t="n">
         <v>0.9967373572593801</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F28" s="12" t="n">
         <v>0.04241435562805873</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -3808,19 +3810,19 @@
           <t>Melia</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="11" t="n">
         <v>462</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="11" t="n">
         <v>18</v>
       </c>
       <c r="D29" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="12" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="12" t="n">
         <v>0.03896103896103896</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -3840,19 +3842,19 @@
           <t>Emporio</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="11" t="n">
         <v>400</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="11" t="n">
         <v>15</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>399</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="12" t="n">
         <v>0.9975000000000001</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F30" s="12" t="n">
         <v>0.0375</v>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -3872,19 +3874,19 @@
           <t>PAM Hotels</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="11" t="n">
         <v>390</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="11" t="n">
         <v>15</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>389</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="12" t="n">
         <v>0.9974358974358974</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="F31" s="12" t="n">
         <v>0.03846153846153846</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3904,19 +3906,19 @@
           <t>Krystal</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="11" t="n">
         <v>388</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C32" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>383</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" s="12" t="n">
         <v>0.9871134020618557</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F32" s="12" t="n">
         <v>0.03350515463917526</v>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -3936,19 +3938,19 @@
           <t>CHOICE</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="11" t="n">
         <v>368</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" s="11" t="n">
         <v>8</v>
       </c>
       <c r="D33" s="5" t="n">
         <v>362</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="12" t="n">
         <v>0.9836956521739131</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F33" s="12" t="n">
         <v>0.02173913043478261</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3968,19 +3970,19 @@
           <t>GRUPO POSADAS</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="11" t="n">
         <v>320</v>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C34" s="11" t="n">
         <v>19</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>320</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F34" s="12" t="n">
         <v>0.059375</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -4000,19 +4002,19 @@
           <t>Decameron</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="11" t="n">
         <v>289</v>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" s="11" t="n">
         <v>49</v>
       </c>
       <c r="D35" s="5" t="n">
         <v>276</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E35" s="12" t="n">
         <v>0.9550173010380623</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="F35" s="12" t="n">
         <v>0.1695501730103806</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -4032,19 +4034,19 @@
           <t>Camino Real</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="11" t="n">
         <v>243</v>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C36" s="11" t="n">
         <v>76</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>243</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="F36" s="12" t="n">
         <v>0.3127572016460906</v>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -4064,19 +4066,19 @@
           <t>Ocean by H10</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="11" t="n">
         <v>232</v>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C37" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="5" t="n">
         <v>149</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="12" t="n">
         <v>0.6422413793103449</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="F37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -4096,19 +4098,19 @@
           <t>Presidente Intercontinental</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B38" s="11" t="n">
         <v>229</v>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C38" s="11" t="n">
         <v>32</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>197</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E38" s="12" t="n">
         <v>0.8602620087336245</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="12" t="n">
         <v>0.1397379912663755</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -4128,19 +4130,19 @@
           <t>Sandos</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="11" t="n">
         <v>177</v>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C39" s="11" t="n">
         <v>15</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>177</v>
       </c>
-      <c r="E39" s="5" t="n">
+      <c r="E39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="F39" s="12" t="n">
         <v>0.0847457627118644</v>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -4160,19 +4162,19 @@
           <t>Iberostar</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="11" t="n">
         <v>171</v>
       </c>
-      <c r="C40" s="5" t="n">
+      <c r="C40" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E40" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="F40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -4192,19 +4194,19 @@
           <t>Hoteles Solar</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="11" t="n">
         <v>164</v>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C41" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D41" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E41" s="12" t="n">
         <v>0.573170731707317</v>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="F41" s="12" t="n">
         <v>0.01829268292682927</v>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -4252,7 +4254,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -4304,19 +4306,19 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="11" t="n">
         <v>15502</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="11" t="n">
         <v>409</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>12523</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="12" t="n">
         <v>0.8078312475809573</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="12" t="n">
         <v>0.02638369242678364</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -4336,19 +4338,19 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="11" t="n">
         <v>8539</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="11" t="n">
         <v>88</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>8077</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="12" t="n">
         <v>0.9458953038997541</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="12" t="n">
         <v>0.01030565640004684</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -4368,19 +4370,19 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="11" t="n">
         <v>6997</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="11" t="n">
         <v>329</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>6329</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="12" t="n">
         <v>0.904530513077033</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="12" t="n">
         <v>0.04702015149349721</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -4400,19 +4402,19 @@
           <t>Riviera Maya</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="11" t="n">
         <v>6705</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="11" t="n">
         <v>369</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>6621</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="12" t="n">
         <v>0.9874720357941834</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="12" t="n">
         <v>0.05503355704697987</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -4432,19 +4434,19 @@
           <t>Londres</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="11" t="n">
         <v>5307</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="11" t="n">
         <v>99</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>4445</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="12" t="n">
         <v>0.8375730167703034</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="12" t="n">
         <v>0.01865460712266817</v>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -4464,19 +4466,19 @@
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="11" t="n">
         <v>4751</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="11" t="n">
         <v>43</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>4710</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="12" t="n">
         <v>0.9913702378446643</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="12" t="n">
         <v>0.00905072616291307</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -4496,19 +4498,19 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="11" t="n">
         <v>3869</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="11" t="n">
         <v>49</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>3774</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="12" t="n">
         <v>0.975445851641251</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="12" t="n">
         <v>0.01266477125872318</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -4528,19 +4530,19 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="11" t="n">
         <v>3262</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="11" t="n">
         <v>71</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>3139</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="12" t="n">
         <v>0.9622930717351318</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="12" t="n">
         <v>0.02176578786020846</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -4560,19 +4562,19 @@
           <t>Punta Cana</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="11" t="n">
         <v>3105</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="11" t="n">
         <v>183</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>2988</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="12" t="n">
         <v>0.9623188405797102</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="12" t="n">
         <v>0.05893719806763285</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -4592,19 +4594,19 @@
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="11" t="n">
         <v>2643</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="11" t="n">
         <v>243</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>2196</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="12" t="n">
         <v>0.8308740068104427</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="12" t="n">
         <v>0.09194097616345062</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -4624,19 +4626,19 @@
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="11" t="n">
         <v>2280</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="11" t="n">
         <v>151</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>1832</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="12" t="n">
         <v>0.8035087719298246</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="12" t="n">
         <v>0.06622807017543859</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -4656,19 +4658,19 @@
           <t>Boston</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="11" t="n">
         <v>2273</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="11" t="n">
         <v>31</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>2216</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="12" t="n">
         <v>0.9749230092388913</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="12" t="n">
         <v>0.01363836339639243</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -4688,19 +4690,19 @@
           <t>Edinburgh Area</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="11" t="n">
         <v>2239</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="11" t="n">
         <v>54</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>1974</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="12" t="n">
         <v>0.8816435908887896</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="12" t="n">
         <v>0.0241179097811523</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -4720,19 +4722,19 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="11" t="n">
         <v>2236</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>1920</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="12" t="n">
         <v>0.8586762075134168</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="12" t="n">
         <v>0.01520572450805009</v>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -4752,19 +4754,19 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="11" t="n">
         <v>1842</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>1757</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="12" t="n">
         <v>0.9538545059717698</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="12" t="n">
         <v>0.006514657980456026</v>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -4784,19 +4786,19 @@
           <t>Tokyo</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="11" t="n">
         <v>1791</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="11" t="n">
         <v>18</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>1499</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E21" s="12" t="n">
         <v>0.836962590731435</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F21" s="12" t="n">
         <v>0.01005025125628141</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -4816,19 +4818,19 @@
           <t>Osaka Area</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="11" t="n">
         <v>1716</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="11" t="n">
         <v>27</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>1523</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="12" t="n">
         <v>0.8875291375291375</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F22" s="12" t="n">
         <v>0.01573426573426574</v>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -4848,19 +4850,19 @@
           <t>Seattle Area</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="11" t="n">
         <v>1562</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="11" t="n">
         <v>67</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>1524</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="12" t="n">
         <v>0.9756722151088348</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="12" t="n">
         <v>0.04289372599231754</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -4880,19 +4882,19 @@
           <t>Madrid</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="11" t="n">
         <v>1544</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="11" t="n">
         <v>29</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>1478</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="12" t="n">
         <v>0.9572538860103627</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="12" t="n">
         <v>0.01878238341968912</v>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -4912,19 +4914,19 @@
           <t>Puerto Vallarta Area</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="11" t="n">
         <v>1348</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="11" t="n">
         <v>60</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>1273</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="12" t="n">
         <v>0.9443620178041543</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="12" t="n">
         <v>0.04451038575667656</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -4944,19 +4946,19 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="11" t="n">
         <v>1257</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="11" t="n">
         <v>25</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>1213</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="12" t="n">
         <v>0.9649960222752586</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" s="12" t="n">
         <v>0.01988862370723946</v>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -4976,19 +4978,19 @@
           <t>San Diego</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="11" t="n">
         <v>1239</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>1074</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="12" t="n">
         <v>0.8668280871670703</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="12" t="n">
         <v>0.002421307506053269</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -5008,19 +5010,19 @@
           <t>Honolulu Area</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="11" t="n">
         <v>1230</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="11" t="n">
         <v>27</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>1176</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="12" t="n">
         <v>0.9560975609756097</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F28" s="12" t="n">
         <v>0.02195121951219512</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -5040,19 +5042,19 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="11" t="n">
         <v>1169</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="11" t="n">
         <v>20</v>
       </c>
       <c r="D29" s="5" t="n">
         <v>1132</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="12" t="n">
         <v>0.9683490162532079</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="12" t="n">
         <v>0.01710863986313088</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -5072,19 +5074,19 @@
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="11" t="n">
         <v>1083</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="11" t="n">
         <v>21</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>1073</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="12" t="n">
         <v>0.9907663896583564</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F30" s="12" t="n">
         <v>0.01939058171745152</v>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -5104,19 +5106,19 @@
           <t>Múnich Area</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="11" t="n">
         <v>947</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="11" t="n">
         <v>40</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>863</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="12" t="n">
         <v>0.91129883843717</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="F31" s="12" t="n">
         <v>0.04223864836325238</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -5136,19 +5138,19 @@
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="11" t="n">
         <v>938</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C32" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>912</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" s="12" t="n">
         <v>0.9722814498933902</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F32" s="12" t="n">
         <v>0.003198294243070362</v>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -5168,19 +5170,19 @@
           <t>Hamburg Area</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="11" t="n">
         <v>917</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" s="11" t="n">
         <v>25</v>
       </c>
       <c r="D33" s="5" t="n">
         <v>893</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="12" t="n">
         <v>0.9738276990185387</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F33" s="12" t="n">
         <v>0.02726281352235551</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -5200,19 +5202,19 @@
           <t>Puerto Rico</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="11" t="n">
         <v>913</v>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C34" s="11" t="n">
         <v>6</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>911</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="12" t="n">
         <v>0.9978094194961665</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F34" s="12" t="n">
         <v>0.006571741511500548</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -5232,19 +5234,19 @@
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="11" t="n">
         <v>905</v>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D35" s="5" t="n">
         <v>843</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E35" s="12" t="n">
         <v>0.9314917127071823</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="F35" s="12" t="n">
         <v>0.007734806629834255</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -5264,19 +5266,19 @@
           <t>Niagara Falls, Canada</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="11" t="n">
         <v>847</v>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C36" s="11" t="n">
         <v>6</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>842</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E36" s="12" t="n">
         <v>0.9940968122786304</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="F36" s="12" t="n">
         <v>0.007083825265643448</v>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -5296,19 +5298,19 @@
           <t>Huatulco Area</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="11" t="n">
         <v>822</v>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C37" s="11" t="n">
         <v>56</v>
       </c>
       <c r="D37" s="5" t="n">
         <v>804</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="12" t="n">
         <v>0.9781021897810219</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="F37" s="12" t="n">
         <v>0.06812652068126521</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -5328,19 +5330,19 @@
           <t>Mexico City - Central Mexico</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B38" s="11" t="n">
         <v>755</v>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C38" s="11" t="n">
         <v>115</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>755</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="12" t="n">
         <v>0.152317880794702</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -5360,19 +5362,19 @@
           <t>Atlanta Area</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="11" t="n">
         <v>746</v>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C39" s="11" t="n">
         <v>14</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>731</v>
       </c>
-      <c r="E39" s="5" t="n">
+      <c r="E39" s="12" t="n">
         <v>0.9798927613941019</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="F39" s="12" t="n">
         <v>0.01876675603217158</v>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -5392,19 +5394,19 @@
           <t>Anaheim Area</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="11" t="n">
         <v>742</v>
       </c>
-      <c r="C40" s="5" t="n">
+      <c r="C40" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>697</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E40" s="12" t="n">
         <v>0.9393530997304582</v>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="F40" s="12" t="n">
         <v>0.004043126684636119</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -5424,19 +5426,19 @@
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="11" t="n">
         <v>732</v>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C41" s="11" t="n">
         <v>4</v>
       </c>
       <c r="D41" s="5" t="n">
         <v>728</v>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E41" s="12" t="n">
         <v>0.9945355191256831</v>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="F41" s="12" t="n">
         <v>0.00546448087431694</v>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -5456,19 +5458,19 @@
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B42" s="11" t="n">
         <v>727</v>
       </c>
-      <c r="C42" s="5" t="n">
+      <c r="C42" s="11" t="n">
         <v>11</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>718</v>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E42" s="12" t="n">
         <v>0.9876203576341128</v>
       </c>
-      <c r="F42" s="5" t="n">
+      <c r="F42" s="12" t="n">
         <v>0.01513067400275103</v>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -5488,19 +5490,19 @@
           <t>Atenas</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B43" s="11" t="n">
         <v>706</v>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C43" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>637</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E43" s="12" t="n">
         <v>0.9022662889518414</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="F43" s="12" t="n">
         <v>0.00424929178470255</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -5520,19 +5522,19 @@
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="B44" s="11" t="n">
         <v>702</v>
       </c>
-      <c r="C44" s="5" t="n">
+      <c r="C44" s="11" t="n">
         <v>23</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>698</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E44" s="12" t="n">
         <v>0.9943019943019943</v>
       </c>
-      <c r="F44" s="5" t="n">
+      <c r="F44" s="12" t="n">
         <v>0.03276353276353276</v>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -5552,19 +5554,19 @@
           <t>Manchester Area</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n">
+      <c r="B45" s="11" t="n">
         <v>653</v>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C45" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D45" s="5" t="n">
         <v>614</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E45" s="12" t="n">
         <v>0.9402756508422665</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="12" t="n">
         <v>0.01990811638591118</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -5584,19 +5586,19 @@
           <t>Nashville (and vicinity), TN, US</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B46" s="11" t="n">
         <v>612</v>
       </c>
-      <c r="C46" s="5" t="n">
+      <c r="C46" s="11" t="n">
         <v>19</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>607</v>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="E46" s="12" t="n">
         <v>0.9918300653594772</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="F46" s="12" t="n">
         <v>0.03104575163398693</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -5616,19 +5618,19 @@
           <t>Tbilisi Area</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n">
+      <c r="B47" s="11" t="n">
         <v>607</v>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C47" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="5" t="n">
         <v>556</v>
       </c>
-      <c r="E47" s="5" t="n">
+      <c r="E47" s="12" t="n">
         <v>0.9159802306425041</v>
       </c>
-      <c r="F47" s="5" t="n">
+      <c r="F47" s="12" t="n">
         <v>0.001647446457990115</v>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -5648,19 +5650,19 @@
           <t>Aruba</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B48" s="11" t="n">
         <v>584</v>
       </c>
-      <c r="C48" s="5" t="n">
+      <c r="C48" s="11" t="n">
         <v>11</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>555</v>
       </c>
-      <c r="E48" s="5" t="n">
+      <c r="E48" s="12" t="n">
         <v>0.9503424657534246</v>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="F48" s="12" t="n">
         <v>0.01883561643835616</v>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -5680,19 +5682,19 @@
           <t>Vienna Area</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B49" s="11" t="n">
         <v>583</v>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C49" s="11" t="n">
         <v>32</v>
       </c>
       <c r="D49" s="5" t="n">
         <v>574</v>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="E49" s="12" t="n">
         <v>0.9845626072041166</v>
       </c>
-      <c r="F49" s="5" t="n">
+      <c r="F49" s="12" t="n">
         <v>0.0548885077186964</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -5712,19 +5714,19 @@
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="B50" s="5" t="n">
+      <c r="B50" s="11" t="n">
         <v>570</v>
       </c>
-      <c r="C50" s="5" t="n">
+      <c r="C50" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>550</v>
       </c>
-      <c r="E50" s="5" t="n">
+      <c r="E50" s="12" t="n">
         <v>0.9649122807017544</v>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="F50" s="12" t="n">
         <v>0.003508771929824561</v>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -5744,19 +5746,19 @@
           <t>New Orleans</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B51" s="11" t="n">
         <v>553</v>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C51" s="11" t="n">
         <v>6</v>
       </c>
       <c r="D51" s="5" t="n">
         <v>528</v>
       </c>
-      <c r="E51" s="5" t="n">
+      <c r="E51" s="12" t="n">
         <v>0.9547920433996383</v>
       </c>
-      <c r="F51" s="5" t="n">
+      <c r="F51" s="12" t="n">
         <v>0.0108499095840868</v>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -5776,19 +5778,19 @@
           <t>Montreal</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B52" s="11" t="n">
         <v>533</v>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C52" s="11" t="n">
         <v>12</v>
       </c>
       <c r="D52" s="5" t="n">
         <v>408</v>
       </c>
-      <c r="E52" s="5" t="n">
+      <c r="E52" s="12" t="n">
         <v>0.7654784240150094</v>
       </c>
-      <c r="F52" s="5" t="n">
+      <c r="F52" s="12" t="n">
         <v>0.0225140712945591</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -5808,19 +5810,19 @@
           <t>Greater Glasgow Area</t>
         </is>
       </c>
-      <c r="B53" s="5" t="n">
+      <c r="B53" s="11" t="n">
         <v>522</v>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C53" s="11" t="n">
         <v>11</v>
       </c>
       <c r="D53" s="5" t="n">
         <v>487</v>
       </c>
-      <c r="E53" s="5" t="n">
+      <c r="E53" s="12" t="n">
         <v>0.9329501915708812</v>
       </c>
-      <c r="F53" s="5" t="n">
+      <c r="F53" s="12" t="n">
         <v>0.0210727969348659</v>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -5840,19 +5842,19 @@
           <t>Dallas</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n">
+      <c r="B54" s="11" t="n">
         <v>514</v>
       </c>
-      <c r="C54" s="5" t="n">
+      <c r="C54" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>497</v>
       </c>
-      <c r="E54" s="5" t="n">
+      <c r="E54" s="12" t="n">
         <v>0.9669260700389105</v>
       </c>
-      <c r="F54" s="5" t="n">
+      <c r="F54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -5872,19 +5874,19 @@
           <t>Jakarta Area</t>
         </is>
       </c>
-      <c r="B55" s="5" t="n">
+      <c r="B55" s="11" t="n">
         <v>508</v>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C55" s="11" t="n">
         <v>26</v>
       </c>
       <c r="D55" s="5" t="n">
         <v>408</v>
       </c>
-      <c r="E55" s="5" t="n">
+      <c r="E55" s="12" t="n">
         <v>0.8031496062992126</v>
       </c>
-      <c r="F55" s="5" t="n">
+      <c r="F55" s="12" t="n">
         <v>0.05118110236220472</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -5904,19 +5906,19 @@
           <t>Antalya Area</t>
         </is>
       </c>
-      <c r="B56" s="5" t="n">
+      <c r="B56" s="11" t="n">
         <v>493</v>
       </c>
-      <c r="C56" s="5" t="n">
+      <c r="C56" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>490</v>
       </c>
-      <c r="E56" s="5" t="n">
+      <c r="E56" s="12" t="n">
         <v>0.9939148073022313</v>
       </c>
-      <c r="F56" s="5" t="n">
+      <c r="F56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -5936,19 +5938,19 @@
           <t>Halifax Area</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n">
+      <c r="B57" s="11" t="n">
         <v>459</v>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C57" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D57" s="5" t="n">
         <v>443</v>
       </c>
-      <c r="E57" s="5" t="n">
+      <c r="E57" s="12" t="n">
         <v>0.9651416122004357</v>
       </c>
-      <c r="F57" s="5" t="n">
+      <c r="F57" s="12" t="n">
         <v>0.02832244008714597</v>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -5968,19 +5970,19 @@
           <t>Jamaica</t>
         </is>
       </c>
-      <c r="B58" s="5" t="n">
+      <c r="B58" s="11" t="n">
         <v>419</v>
       </c>
-      <c r="C58" s="5" t="n">
+      <c r="C58" s="11" t="n">
         <v>24</v>
       </c>
       <c r="D58" s="5" t="n">
         <v>248</v>
       </c>
-      <c r="E58" s="5" t="n">
+      <c r="E58" s="12" t="n">
         <v>0.5918854415274463</v>
       </c>
-      <c r="F58" s="5" t="n">
+      <c r="F58" s="12" t="n">
         <v>0.05727923627684964</v>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -6000,19 +6002,19 @@
           <t>SinClasificar</t>
         </is>
       </c>
-      <c r="B59" s="5" t="n">
+      <c r="B59" s="11" t="n">
         <v>418</v>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C59" s="11" t="n">
         <v>5</v>
       </c>
       <c r="D59" s="5" t="n">
         <v>363</v>
       </c>
-      <c r="E59" s="5" t="n">
+      <c r="E59" s="12" t="n">
         <v>0.868421052631579</v>
       </c>
-      <c r="F59" s="5" t="n">
+      <c r="F59" s="12" t="n">
         <v>0.01196172248803828</v>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -6032,19 +6034,19 @@
           <t>Liverpool</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n">
+      <c r="B60" s="11" t="n">
         <v>406</v>
       </c>
-      <c r="C60" s="5" t="n">
+      <c r="C60" s="11" t="n">
         <v>6</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>369</v>
       </c>
-      <c r="E60" s="5" t="n">
+      <c r="E60" s="12" t="n">
         <v>0.9088669950738916</v>
       </c>
-      <c r="F60" s="5" t="n">
+      <c r="F60" s="12" t="n">
         <v>0.01477832512315271</v>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -6064,19 +6066,19 @@
           <t>London Area</t>
         </is>
       </c>
-      <c r="B61" s="5" t="n">
+      <c r="B61" s="11" t="n">
         <v>406</v>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C61" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D61" s="5" t="n">
         <v>353</v>
       </c>
-      <c r="E61" s="5" t="n">
+      <c r="E61" s="12" t="n">
         <v>0.8694581280788177</v>
       </c>
-      <c r="F61" s="5" t="n">
+      <c r="F61" s="12" t="n">
         <v>0.01724137931034483</v>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -6096,19 +6098,19 @@
           <t>Phu Quoc Island Area</t>
         </is>
       </c>
-      <c r="B62" s="5" t="n">
+      <c r="B62" s="11" t="n">
         <v>398</v>
       </c>
-      <c r="C62" s="5" t="n">
+      <c r="C62" s="11" t="n">
         <v>5</v>
       </c>
       <c r="D62" s="5" t="n">
         <v>355</v>
       </c>
-      <c r="E62" s="5" t="n">
+      <c r="E62" s="12" t="n">
         <v>0.8919597989949749</v>
       </c>
-      <c r="F62" s="5" t="n">
+      <c r="F62" s="12" t="n">
         <v>0.01256281407035176</v>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -6128,19 +6130,19 @@
           <t>Mazatlán</t>
         </is>
       </c>
-      <c r="B63" s="5" t="n">
+      <c r="B63" s="11" t="n">
         <v>396</v>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C63" s="11" t="n">
         <v>12</v>
       </c>
       <c r="D63" s="5" t="n">
         <v>396</v>
       </c>
-      <c r="E63" s="5" t="n">
+      <c r="E63" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F63" s="5" t="n">
+      <c r="F63" s="12" t="n">
         <v>0.0303030303030303</v>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -6160,19 +6162,19 @@
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="B64" s="5" t="n">
+      <c r="B64" s="11" t="n">
         <v>393</v>
       </c>
-      <c r="C64" s="5" t="n">
+      <c r="C64" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D64" s="5" t="n">
         <v>355</v>
       </c>
-      <c r="E64" s="5" t="n">
+      <c r="E64" s="12" t="n">
         <v>0.9033078880407125</v>
       </c>
-      <c r="F64" s="5" t="n">
+      <c r="F64" s="12" t="n">
         <v>0.0178117048346056</v>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -6192,19 +6194,19 @@
           <t>Chiba Area</t>
         </is>
       </c>
-      <c r="B65" s="5" t="n">
+      <c r="B65" s="11" t="n">
         <v>390</v>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C65" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D65" s="5" t="n">
         <v>377</v>
       </c>
-      <c r="E65" s="5" t="n">
+      <c r="E65" s="12" t="n">
         <v>0.9666666666666667</v>
       </c>
-      <c r="F65" s="5" t="n">
+      <c r="F65" s="12" t="n">
         <v>0.01794871794871795</v>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -6224,19 +6226,19 @@
           <t>French Riviera Area</t>
         </is>
       </c>
-      <c r="B66" s="5" t="n">
+      <c r="B66" s="11" t="n">
         <v>372</v>
       </c>
-      <c r="C66" s="5" t="n">
+      <c r="C66" s="11" t="n">
         <v>6</v>
       </c>
       <c r="D66" s="5" t="n">
         <v>360</v>
       </c>
-      <c r="E66" s="5" t="n">
+      <c r="E66" s="12" t="n">
         <v>0.967741935483871</v>
       </c>
-      <c r="F66" s="5" t="n">
+      <c r="F66" s="12" t="n">
         <v>0.01612903225806452</v>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -6256,19 +6258,19 @@
           <t>Hakone Area</t>
         </is>
       </c>
-      <c r="B67" s="5" t="n">
+      <c r="B67" s="11" t="n">
         <v>370</v>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C67" s="11" t="n">
         <v>5</v>
       </c>
       <c r="D67" s="5" t="n">
         <v>365</v>
       </c>
-      <c r="E67" s="5" t="n">
+      <c r="E67" s="12" t="n">
         <v>0.9864864864864865</v>
       </c>
-      <c r="F67" s="5" t="n">
+      <c r="F67" s="12" t="n">
         <v>0.01351351351351351</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -6288,19 +6290,19 @@
           <t>Dresde Area</t>
         </is>
       </c>
-      <c r="B68" s="5" t="n">
+      <c r="B68" s="11" t="n">
         <v>367</v>
       </c>
-      <c r="C68" s="5" t="n">
+      <c r="C68" s="11" t="n">
         <v>9</v>
       </c>
       <c r="D68" s="5" t="n">
         <v>351</v>
       </c>
-      <c r="E68" s="5" t="n">
+      <c r="E68" s="12" t="n">
         <v>0.9564032697547684</v>
       </c>
-      <c r="F68" s="5" t="n">
+      <c r="F68" s="12" t="n">
         <v>0.02452316076294278</v>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -6320,19 +6322,19 @@
           <t>Acapulco</t>
         </is>
       </c>
-      <c r="B69" s="5" t="n">
+      <c r="B69" s="11" t="n">
         <v>365</v>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C69" s="11" t="n">
         <v>15</v>
       </c>
       <c r="D69" s="5" t="n">
         <v>272</v>
       </c>
-      <c r="E69" s="5" t="n">
+      <c r="E69" s="12" t="n">
         <v>0.7452054794520548</v>
       </c>
-      <c r="F69" s="5" t="n">
+      <c r="F69" s="12" t="n">
         <v>0.0410958904109589</v>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -6352,19 +6354,19 @@
           <t>Ottawa Area</t>
         </is>
       </c>
-      <c r="B70" s="5" t="n">
+      <c r="B70" s="11" t="n">
         <v>360</v>
       </c>
-      <c r="C70" s="5" t="n">
+      <c r="C70" s="11" t="n">
         <v>9</v>
       </c>
       <c r="D70" s="5" t="n">
         <v>297</v>
       </c>
-      <c r="E70" s="5" t="n">
+      <c r="E70" s="12" t="n">
         <v>0.825</v>
       </c>
-      <c r="F70" s="5" t="n">
+      <c r="F70" s="12" t="n">
         <v>0.025</v>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -6384,19 +6386,19 @@
           <t>Phoenix (and vicinity), AZ, US</t>
         </is>
       </c>
-      <c r="B71" s="5" t="n">
+      <c r="B71" s="11" t="n">
         <v>346</v>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C71" s="11" t="n">
         <v>6</v>
       </c>
       <c r="D71" s="5" t="n">
         <v>344</v>
       </c>
-      <c r="E71" s="5" t="n">
+      <c r="E71" s="12" t="n">
         <v>0.9942196531791907</v>
       </c>
-      <c r="F71" s="5" t="n">
+      <c r="F71" s="12" t="n">
         <v>0.01734104046242774</v>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -6416,19 +6418,19 @@
           <t>Los Cabos Area</t>
         </is>
       </c>
-      <c r="B72" s="5" t="n">
+      <c r="B72" s="11" t="n">
         <v>338</v>
       </c>
-      <c r="C72" s="5" t="n">
+      <c r="C72" s="11" t="n">
         <v>31</v>
       </c>
       <c r="D72" s="5" t="n">
         <v>338</v>
       </c>
-      <c r="E72" s="5" t="n">
+      <c r="E72" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F72" s="5" t="n">
+      <c r="F72" s="12" t="n">
         <v>0.09171597633136094</v>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -6448,19 +6450,19 @@
           <t>Lake Constance Area</t>
         </is>
       </c>
-      <c r="B73" s="5" t="n">
+      <c r="B73" s="11" t="n">
         <v>337</v>
       </c>
-      <c r="C73" s="5" t="n">
+      <c r="C73" s="11" t="n">
         <v>54</v>
       </c>
       <c r="D73" s="5" t="n">
         <v>330</v>
       </c>
-      <c r="E73" s="5" t="n">
+      <c r="E73" s="12" t="n">
         <v>0.9792284866468842</v>
       </c>
-      <c r="F73" s="5" t="n">
+      <c r="F73" s="12" t="n">
         <v>0.1602373887240356</v>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -6480,19 +6482,19 @@
           <t>Cozumel</t>
         </is>
       </c>
-      <c r="B74" s="5" t="n">
+      <c r="B74" s="11" t="n">
         <v>335</v>
       </c>
-      <c r="C74" s="5" t="n">
+      <c r="C74" s="11" t="n">
         <v>28</v>
       </c>
       <c r="D74" s="5" t="n">
         <v>335</v>
       </c>
-      <c r="E74" s="5" t="n">
+      <c r="E74" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F74" s="5" t="n">
+      <c r="F74" s="12" t="n">
         <v>0.08358208955223881</v>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -6512,19 +6514,19 @@
           <t>Fráncfort</t>
         </is>
       </c>
-      <c r="B75" s="5" t="n">
+      <c r="B75" s="11" t="n">
         <v>326</v>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C75" s="11" t="n">
         <v>5</v>
       </c>
       <c r="D75" s="5" t="n">
         <v>277</v>
       </c>
-      <c r="E75" s="5" t="n">
+      <c r="E75" s="12" t="n">
         <v>0.8496932515337423</v>
       </c>
-      <c r="F75" s="5" t="n">
+      <c r="F75" s="12" t="n">
         <v>0.01533742331288344</v>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -6544,19 +6546,19 @@
           <t>Nueva Delhi Area</t>
         </is>
       </c>
-      <c r="B76" s="5" t="n">
+      <c r="B76" s="11" t="n">
         <v>323</v>
       </c>
-      <c r="C76" s="5" t="n">
+      <c r="C76" s="11" t="n">
         <v>6</v>
       </c>
       <c r="D76" s="5" t="n">
         <v>323</v>
       </c>
-      <c r="E76" s="5" t="n">
+      <c r="E76" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F76" s="5" t="n">
+      <c r="F76" s="12" t="n">
         <v>0.01857585139318885</v>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -6576,19 +6578,19 @@
           <t>Bath Area</t>
         </is>
       </c>
-      <c r="B77" s="5" t="n">
+      <c r="B77" s="11" t="n">
         <v>321</v>
       </c>
-      <c r="C77" s="5" t="n">
+      <c r="C77" s="11" t="n">
         <v>10</v>
       </c>
       <c r="D77" s="5" t="n">
         <v>317</v>
       </c>
-      <c r="E77" s="5" t="n">
+      <c r="E77" s="12" t="n">
         <v>0.9875389408099688</v>
       </c>
-      <c r="F77" s="5" t="n">
+      <c r="F77" s="12" t="n">
         <v>0.03115264797507788</v>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -6608,19 +6610,19 @@
           <t>Melbourne Area</t>
         </is>
       </c>
-      <c r="B78" s="5" t="n">
+      <c r="B78" s="11" t="n">
         <v>317</v>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C78" s="11" t="n">
         <v>41</v>
       </c>
       <c r="D78" s="5" t="n">
         <v>207</v>
       </c>
-      <c r="E78" s="5" t="n">
+      <c r="E78" s="12" t="n">
         <v>0.6529968454258676</v>
       </c>
-      <c r="F78" s="5" t="n">
+      <c r="F78" s="12" t="n">
         <v>0.1293375394321767</v>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -6640,19 +6642,19 @@
           <t>Budapest Area</t>
         </is>
       </c>
-      <c r="B79" s="5" t="n">
+      <c r="B79" s="11" t="n">
         <v>317</v>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C79" s="11" t="n">
         <v>10</v>
       </c>
       <c r="D79" s="5" t="n">
         <v>308</v>
       </c>
-      <c r="E79" s="5" t="n">
+      <c r="E79" s="12" t="n">
         <v>0.9716088328075709</v>
       </c>
-      <c r="F79" s="5" t="n">
+      <c r="F79" s="12" t="n">
         <v>0.03154574132492113</v>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -6672,19 +6674,19 @@
           <t>Okanagan Valley Area</t>
         </is>
       </c>
-      <c r="B80" s="5" t="n">
+      <c r="B80" s="11" t="n">
         <v>313</v>
       </c>
-      <c r="C80" s="5" t="n">
+      <c r="C80" s="11" t="n">
         <v>4</v>
       </c>
       <c r="D80" s="5" t="n">
         <v>296</v>
       </c>
-      <c r="E80" s="5" t="n">
+      <c r="E80" s="12" t="n">
         <v>0.9456869009584664</v>
       </c>
-      <c r="F80" s="5" t="n">
+      <c r="F80" s="12" t="n">
         <v>0.01277955271565495</v>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -6704,19 +6706,19 @@
           <t>Malaga Area</t>
         </is>
       </c>
-      <c r="B81" s="5" t="n">
+      <c r="B81" s="11" t="n">
         <v>309</v>
       </c>
-      <c r="C81" s="5" t="n">
+      <c r="C81" s="11" t="n">
         <v>5</v>
       </c>
       <c r="D81" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="E81" s="5" t="n">
+      <c r="E81" s="12" t="n">
         <v>0.9838187702265372</v>
       </c>
-      <c r="F81" s="5" t="n">
+      <c r="F81" s="12" t="n">
         <v>0.01618122977346278</v>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -6736,19 +6738,19 @@
           <t>Hampton Roads</t>
         </is>
       </c>
-      <c r="B82" s="5" t="n">
+      <c r="B82" s="11" t="n">
         <v>305</v>
       </c>
-      <c r="C82" s="5" t="n">
+      <c r="C82" s="11" t="n">
         <v>5</v>
       </c>
       <c r="D82" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="E82" s="5" t="n">
+      <c r="E82" s="12" t="n">
         <v>0.9967213114754099</v>
       </c>
-      <c r="F82" s="5" t="n">
+      <c r="F82" s="12" t="n">
         <v>0.01639344262295082</v>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -6768,19 +6770,19 @@
           <t>West Sussex Area</t>
         </is>
       </c>
-      <c r="B83" s="5" t="n">
+      <c r="B83" s="11" t="n">
         <v>302</v>
       </c>
-      <c r="C83" s="5" t="n">
+      <c r="C83" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="E83" s="5" t="n">
+      <c r="E83" s="12" t="n">
         <v>0.9933774834437086</v>
       </c>
-      <c r="F83" s="5" t="n">
+      <c r="F83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -6800,19 +6802,19 @@
           <t>Munich Area</t>
         </is>
       </c>
-      <c r="B84" s="5" t="n">
+      <c r="B84" s="11" t="n">
         <v>269</v>
       </c>
-      <c r="C84" s="5" t="n">
+      <c r="C84" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D84" s="5" t="n">
         <v>267</v>
       </c>
-      <c r="E84" s="5" t="n">
+      <c r="E84" s="12" t="n">
         <v>0.9925650557620818</v>
       </c>
-      <c r="F84" s="5" t="n">
+      <c r="F84" s="12" t="n">
         <v>0.02602230483271376</v>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -6832,19 +6834,19 @@
           <t>Brunswick Area</t>
         </is>
       </c>
-      <c r="B85" s="5" t="n">
+      <c r="B85" s="11" t="n">
         <v>261</v>
       </c>
-      <c r="C85" s="5" t="n">
+      <c r="C85" s="11" t="n">
         <v>9</v>
       </c>
       <c r="D85" s="5" t="n">
         <v>252</v>
       </c>
-      <c r="E85" s="5" t="n">
+      <c r="E85" s="12" t="n">
         <v>0.9655172413793104</v>
       </c>
-      <c r="F85" s="5" t="n">
+      <c r="F85" s="12" t="n">
         <v>0.03448275862068965</v>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -6864,19 +6866,19 @@
           <t>Kioto Area</t>
         </is>
       </c>
-      <c r="B86" s="5" t="n">
+      <c r="B86" s="11" t="n">
         <v>258</v>
       </c>
-      <c r="C86" s="5" t="n">
+      <c r="C86" s="11" t="n">
         <v>4</v>
       </c>
       <c r="D86" s="5" t="n">
         <v>258</v>
       </c>
-      <c r="E86" s="5" t="n">
+      <c r="E86" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F86" s="5" t="n">
+      <c r="F86" s="12" t="n">
         <v>0.01550387596899225</v>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -6896,19 +6898,19 @@
           <t>Sharm el Sheikh Area</t>
         </is>
       </c>
-      <c r="B87" s="5" t="n">
+      <c r="B87" s="11" t="n">
         <v>256</v>
       </c>
-      <c r="C87" s="5" t="n">
+      <c r="C87" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="5" t="n">
         <v>256</v>
       </c>
-      <c r="E87" s="5" t="n">
+      <c r="E87" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F87" s="5" t="n">
+      <c r="F87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -6928,19 +6930,19 @@
           <t>Helsinki Area</t>
         </is>
       </c>
-      <c r="B88" s="5" t="n">
+      <c r="B88" s="11" t="n">
         <v>254</v>
       </c>
-      <c r="C88" s="5" t="n">
+      <c r="C88" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D88" s="5" t="n">
         <v>244</v>
       </c>
-      <c r="E88" s="5" t="n">
+      <c r="E88" s="12" t="n">
         <v>0.9606299212598425</v>
       </c>
-      <c r="F88" s="5" t="n">
+      <c r="F88" s="12" t="n">
         <v>0.01181102362204724</v>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -6960,19 +6962,19 @@
           <t>Da Nang Area</t>
         </is>
       </c>
-      <c r="B89" s="5" t="n">
+      <c r="B89" s="11" t="n">
         <v>237</v>
       </c>
-      <c r="C89" s="5" t="n">
+      <c r="C89" s="11" t="n">
         <v>5</v>
       </c>
       <c r="D89" s="5" t="n">
         <v>197</v>
       </c>
-      <c r="E89" s="5" t="n">
+      <c r="E89" s="12" t="n">
         <v>0.8312236286919831</v>
       </c>
-      <c r="F89" s="5" t="n">
+      <c r="F89" s="12" t="n">
         <v>0.02109704641350211</v>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -6992,19 +6994,19 @@
           <t>Hanói Area</t>
         </is>
       </c>
-      <c r="B90" s="5" t="n">
+      <c r="B90" s="11" t="n">
         <v>234</v>
       </c>
-      <c r="C90" s="5" t="n">
+      <c r="C90" s="11" t="n">
         <v>6</v>
       </c>
       <c r="D90" s="5" t="n">
         <v>195</v>
       </c>
-      <c r="E90" s="5" t="n">
+      <c r="E90" s="12" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="F90" s="5" t="n">
+      <c r="F90" s="12" t="n">
         <v>0.02564102564102564</v>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -7024,19 +7026,19 @@
           <t>Milan</t>
         </is>
       </c>
-      <c r="B91" s="5" t="n">
+      <c r="B91" s="11" t="n">
         <v>225</v>
       </c>
-      <c r="C91" s="5" t="n">
+      <c r="C91" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
         <v>224</v>
       </c>
-      <c r="E91" s="5" t="n">
+      <c r="E91" s="12" t="n">
         <v>0.9955555555555555</v>
       </c>
-      <c r="F91" s="5" t="n">
+      <c r="F91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -7056,19 +7058,19 @@
           <t>Madrid Area</t>
         </is>
       </c>
-      <c r="B92" s="5" t="n">
+      <c r="B92" s="11" t="n">
         <v>219</v>
       </c>
-      <c r="C92" s="5" t="n">
+      <c r="C92" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D92" s="5" t="n">
         <v>219</v>
       </c>
-      <c r="E92" s="5" t="n">
+      <c r="E92" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F92" s="5" t="n">
+      <c r="F92" s="12" t="n">
         <v>0.0593607305936073</v>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -7088,19 +7090,19 @@
           <t>Page Area</t>
         </is>
       </c>
-      <c r="B93" s="5" t="n">
+      <c r="B93" s="11" t="n">
         <v>219</v>
       </c>
-      <c r="C93" s="5" t="n">
+      <c r="C93" s="11" t="n">
         <v>10</v>
       </c>
       <c r="D93" s="5" t="n">
         <v>216</v>
       </c>
-      <c r="E93" s="5" t="n">
+      <c r="E93" s="12" t="n">
         <v>0.9863013698630136</v>
       </c>
-      <c r="F93" s="5" t="n">
+      <c r="F93" s="12" t="n">
         <v>0.045662100456621</v>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -7120,19 +7122,19 @@
           <t>Monterey Area</t>
         </is>
       </c>
-      <c r="B94" s="5" t="n">
+      <c r="B94" s="11" t="n">
         <v>217</v>
       </c>
-      <c r="C94" s="5" t="n">
+      <c r="C94" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D94" s="5" t="n">
         <v>199</v>
       </c>
-      <c r="E94" s="5" t="n">
+      <c r="E94" s="12" t="n">
         <v>0.9170506912442397</v>
       </c>
-      <c r="F94" s="5" t="n">
+      <c r="F94" s="12" t="n">
         <v>0.05990783410138249</v>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -7152,19 +7154,19 @@
           <t>Sídney Area</t>
         </is>
       </c>
-      <c r="B95" s="5" t="n">
+      <c r="B95" s="11" t="n">
         <v>209</v>
       </c>
-      <c r="C95" s="5" t="n">
+      <c r="C95" s="11" t="n">
         <v>8</v>
       </c>
       <c r="D95" s="5" t="n">
         <v>173</v>
       </c>
-      <c r="E95" s="5" t="n">
+      <c r="E95" s="12" t="n">
         <v>0.8277511961722488</v>
       </c>
-      <c r="F95" s="5" t="n">
+      <c r="F95" s="12" t="n">
         <v>0.03827751196172249</v>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -7184,19 +7186,19 @@
           <t>North Yorkshire Area</t>
         </is>
       </c>
-      <c r="B96" s="5" t="n">
+      <c r="B96" s="11" t="n">
         <v>208</v>
       </c>
-      <c r="C96" s="5" t="n">
+      <c r="C96" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="5" t="n">
         <v>198</v>
       </c>
-      <c r="E96" s="5" t="n">
+      <c r="E96" s="12" t="n">
         <v>0.9519230769230769</v>
       </c>
-      <c r="F96" s="5" t="n">
+      <c r="F96" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -7216,19 +7218,19 @@
           <t>Ho Chi Minh Area</t>
         </is>
       </c>
-      <c r="B97" s="5" t="n">
+      <c r="B97" s="11" t="n">
         <v>206</v>
       </c>
-      <c r="C97" s="5" t="n">
+      <c r="C97" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D97" s="5" t="n">
         <v>202</v>
       </c>
-      <c r="E97" s="5" t="n">
+      <c r="E97" s="12" t="n">
         <v>0.9805825242718447</v>
       </c>
-      <c r="F97" s="5" t="n">
+      <c r="F97" s="12" t="n">
         <v>0.06310679611650485</v>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -7248,19 +7250,19 @@
           <t>Ventura Area</t>
         </is>
       </c>
-      <c r="B98" s="5" t="n">
+      <c r="B98" s="11" t="n">
         <v>205</v>
       </c>
-      <c r="C98" s="5" t="n">
+      <c r="C98" s="11" t="n">
         <v>20</v>
       </c>
       <c r="D98" s="5" t="n">
         <v>205</v>
       </c>
-      <c r="E98" s="5" t="n">
+      <c r="E98" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F98" s="5" t="n">
+      <c r="F98" s="12" t="n">
         <v>0.0975609756097561</v>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -7280,19 +7282,19 @@
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="B99" s="5" t="n">
+      <c r="B99" s="11" t="n">
         <v>198</v>
       </c>
-      <c r="C99" s="5" t="n">
+      <c r="C99" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D99" s="5" t="n">
         <v>198</v>
       </c>
-      <c r="E99" s="5" t="n">
+      <c r="E99" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F99" s="5" t="n">
+      <c r="F99" s="12" t="n">
         <v>0.005050505050505051</v>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -7312,19 +7314,19 @@
           <t>Newport Beach</t>
         </is>
       </c>
-      <c r="B100" s="5" t="n">
+      <c r="B100" s="11" t="n">
         <v>191</v>
       </c>
-      <c r="C100" s="5" t="n">
+      <c r="C100" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D100" s="5" t="n">
         <v>190</v>
       </c>
-      <c r="E100" s="5" t="n">
+      <c r="E100" s="12" t="n">
         <v>0.9947643979057592</v>
       </c>
-      <c r="F100" s="5" t="n">
+      <c r="F100" s="12" t="n">
         <v>0.01570680628272251</v>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -7344,19 +7346,19 @@
           <t>Hawái</t>
         </is>
       </c>
-      <c r="B101" s="5" t="n">
+      <c r="B101" s="11" t="n">
         <v>186</v>
       </c>
-      <c r="C101" s="5" t="n">
+      <c r="C101" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D101" s="5" t="n">
         <v>186</v>
       </c>
-      <c r="E101" s="5" t="n">
+      <c r="E101" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F101" s="5" t="n">
+      <c r="F101" s="12" t="n">
         <v>0.01075268817204301</v>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -7376,19 +7378,19 @@
           <t>Kingston Area</t>
         </is>
       </c>
-      <c r="B102" s="5" t="n">
+      <c r="B102" s="11" t="n">
         <v>185</v>
       </c>
-      <c r="C102" s="5" t="n">
+      <c r="C102" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D102" s="5" t="n">
         <v>185</v>
       </c>
-      <c r="E102" s="5" t="n">
+      <c r="E102" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F102" s="5" t="n">
+      <c r="F102" s="12" t="n">
         <v>0.01081081081081081</v>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -7408,19 +7410,19 @@
           <t>Washington, DC Area</t>
         </is>
       </c>
-      <c r="B103" s="5" t="n">
+      <c r="B103" s="11" t="n">
         <v>182</v>
       </c>
-      <c r="C103" s="5" t="n">
+      <c r="C103" s="11" t="n">
         <v>4</v>
       </c>
       <c r="D103" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="E103" s="5" t="n">
+      <c r="E103" s="12" t="n">
         <v>0.9890109890109891</v>
       </c>
-      <c r="F103" s="5" t="n">
+      <c r="F103" s="12" t="n">
         <v>0.02197802197802198</v>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -7440,19 +7442,19 @@
           <t>Manzanillo</t>
         </is>
       </c>
-      <c r="B104" s="5" t="n">
+      <c r="B104" s="11" t="n">
         <v>182</v>
       </c>
-      <c r="C104" s="5" t="n">
+      <c r="C104" s="11" t="n">
         <v>5</v>
       </c>
       <c r="D104" s="5" t="n">
         <v>182</v>
       </c>
-      <c r="E104" s="5" t="n">
+      <c r="E104" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F104" s="5" t="n">
+      <c r="F104" s="12" t="n">
         <v>0.02747252747252747</v>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -7472,19 +7474,19 @@
           <t>Núremberg Area</t>
         </is>
       </c>
-      <c r="B105" s="5" t="n">
+      <c r="B105" s="11" t="n">
         <v>177</v>
       </c>
-      <c r="C105" s="5" t="n">
+      <c r="C105" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D105" s="5" t="n">
         <v>176</v>
       </c>
-      <c r="E105" s="5" t="n">
+      <c r="E105" s="12" t="n">
         <v>0.9943502824858758</v>
       </c>
-      <c r="F105" s="5" t="n">
+      <c r="F105" s="12" t="n">
         <v>0.01694915254237288</v>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -7532,7 +7534,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W21 · 18–24 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -7584,19 +7586,19 @@
           <t>DerbySoft</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="11" t="n">
         <v>77965</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="11" t="n">
         <v>1495</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>73308</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="12" t="n">
         <v>0.9402680690053229</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="12" t="n">
         <v>0.01917527095491567</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -7616,19 +7618,19 @@
           <t>Internal</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="11" t="n">
         <v>20708</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="11" t="n">
         <v>1056</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>18842</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="12" t="n">
         <v>0.9098898976241067</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="12" t="n">
         <v>0.05099478462429979</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -7648,19 +7650,19 @@
           <t>HBSI</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="11" t="n">
         <v>15131</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="11" t="n">
         <v>405</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>11748</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="12" t="n">
         <v>0.7764192716938735</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="12" t="n">
         <v>0.02676624149097879</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -7680,19 +7682,19 @@
           <t>SynXis</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="11" t="n">
         <v>3440</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="11" t="n">
         <v>176</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>3322</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="12" t="n">
         <v>0.9656976744186047</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="12" t="n">
         <v>0.05116279069767442</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -7712,19 +7714,19 @@
           <t>Siteminder</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="11" t="n">
         <v>2433</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="11" t="n">
         <v>277</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>2433</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="12" t="n">
         <v>0.1138512124948623</v>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -7744,19 +7746,19 @@
           <t>Expedia</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="11" t="n">
         <v>556</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>553</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="12" t="n">
         <v>0.9946043165467626</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -7776,19 +7778,19 @@
           <t>HotelBeds</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="11" t="n">
         <v>524</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="11" t="n">
         <v>17</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>460</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="12" t="n">
         <v>0.8778625954198473</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="12" t="n">
         <v>0.03244274809160305</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -7808,19 +7810,19 @@
           <t>Travelclick</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="11" t="n">
         <v>243</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="11" t="n">
         <v>76</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>243</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="12" t="n">
         <v>0.3127572016460906</v>
       </c>
       <c r="G13" s="5" t="inlineStr">

--- a/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11644,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -19651,7 +19651,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -21190,7 +21190,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11644,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -19651,7 +19651,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -21190,7 +21190,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11644,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -19651,7 +19651,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -21190,7 +21190,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11644,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -19651,7 +19651,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -21190,7 +21190,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11644,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -19651,7 +19651,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -21190,7 +21190,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11644,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -19651,7 +19651,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -21190,7 +21190,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11644,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -19651,7 +19651,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -21190,7 +21190,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:53 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_CUG_7d.xlsx
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11644,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -19651,7 +19651,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -21190,7 +21190,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W21 · 18–24 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W21 · 18–24 may 2026</t>
         </is>
       </c>
     </row>
